--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20231001_20240401.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20231001_20240401.xlsx
@@ -833,37 +833,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59.01639344262295</v>
+        <v>65.57377049180327</v>
       </c>
       <c r="C10" t="n">
-        <v>40.98360655737705</v>
+        <v>34.42622950819672</v>
       </c>
       <c r="D10" t="n">
-        <v>80.78589990982074</v>
+        <v>61.91176166296459</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>INE094A01015</t>
+          <t>INE271C01023</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>-18.0327868852459</v>
+        <v>-31.14754098360655</v>
       </c>
       <c r="H10" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>54</v>
       </c>
       <c r="J10" t="n">
-        <v>317.1</v>
+        <v>897</v>
       </c>
       <c r="K10" t="n">
         <v>9</v>
@@ -877,37 +877,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>65.57377049180327</v>
+        <v>59.01639344262295</v>
       </c>
       <c r="C11" t="n">
-        <v>34.42622950819672</v>
+        <v>40.98360655737705</v>
       </c>
       <c r="D11" t="n">
-        <v>61.91176166296459</v>
+        <v>80.78589990982074</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>INE271C01023</t>
+          <t>INE094A01015</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>-31.14754098360655</v>
+        <v>-18.0327868852459</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="I11" t="n">
         <v>54</v>
       </c>
       <c r="J11" t="n">
-        <v>897</v>
+        <v>317.1</v>
       </c>
       <c r="K11" t="n">
         <v>10</v>
